--- a/files/SM1/K3/K3-Verb.xlsx
+++ b/files/SM1/K3/K3-Verb.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\finnish-space\files\SM1\K3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{524EED96-E740-4554-AA33-A39CB0AB0FD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{190745B8-D81F-4DAE-A0E5-DAC09407EF3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4050" yWindow="2220" windowWidth="17720" windowHeight="10090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>ampua</t>
   </si>
@@ -147,14 +147,6 @@
   </si>
   <si>
     <t>to stay overnight</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kylpeä</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>to bathe</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -504,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -675,14 +667,6 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
